--- a/artfynd/A 33461-2025 artfynd.xlsx
+++ b/artfynd/A 33461-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1849,6 +1849,118 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126562069</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78647</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hökmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489273</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6688332</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33461-2025 artfynd.xlsx
+++ b/artfynd/A 33461-2025 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>126562069</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 33461-2025 artfynd.xlsx
+++ b/artfynd/A 33461-2025 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>126562069</v>
       </c>
       <c r="B13" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 33461-2025 artfynd.xlsx
+++ b/artfynd/A 33461-2025 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>126562069</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
